--- a/artfynd/A 6629-2024 artfynd.xlsx
+++ b/artfynd/A 6629-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6629-2024 artfynd.xlsx
+++ b/artfynd/A 6629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95637515</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625472.9160379374</v>
+        <v>625473</v>
       </c>
       <c r="R2" t="n">
-        <v>6925342.162208681</v>
+        <v>6925343</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>

--- a/artfynd/A 6629-2024 artfynd.xlsx
+++ b/artfynd/A 6629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95637515</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6629-2024 artfynd.xlsx
+++ b/artfynd/A 6629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95637515</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6629-2024 artfynd.xlsx
+++ b/artfynd/A 6629-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95637515</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
